--- a/Project-QM/QM-CAPS.xlsx
+++ b/Project-QM/QM-CAPS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtinoco2\Downloads\Failures-PMI\Project-QM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2350F67-AD67-465E-A238-B3D4A5E6D507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA134336-8454-4E38-B03A-08957BA720B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{4BDF2B56-9764-4C8B-AF0F-1F7AAACB60FA}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="7270" xr2:uid="{4BDF2B56-9764-4C8B-AF0F-1F7AAACB60FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -906,7 +906,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{812DFA3C-E692-41F9-A0B2-252AE404A69C}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P1034"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -963,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>100</v>
       </c>
@@ -1013,7 +1012,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>100</v>
       </c>
@@ -1063,7 +1062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>100</v>
       </c>
@@ -1113,7 +1112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>100</v>
       </c>
@@ -1163,7 +1162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>100</v>
       </c>
@@ -1213,7 +1212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
@@ -1263,7 +1262,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>100</v>
       </c>
@@ -1313,7 +1312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>100</v>
       </c>
@@ -1363,7 +1362,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>100</v>
       </c>
@@ -1413,7 +1412,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>100</v>
       </c>
@@ -1463,7 +1462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>100</v>
       </c>
@@ -1513,7 +1512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>100</v>
       </c>
@@ -1563,7 +1562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>100</v>
       </c>
@@ -1613,7 +1612,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>100</v>
       </c>
@@ -1663,7 +1662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>100</v>
       </c>
@@ -1713,7 +1712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>100</v>
       </c>
@@ -1763,7 +1762,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>100</v>
       </c>
@@ -1813,7 +1812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>100</v>
       </c>
@@ -1863,7 +1862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>100</v>
       </c>
@@ -1913,7 +1912,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>100</v>
       </c>
@@ -1963,7 +1962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>100</v>
       </c>
@@ -2013,7 +2012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>100</v>
       </c>
@@ -2063,7 +2062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>100</v>
       </c>
@@ -2113,7 +2112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>100</v>
       </c>
@@ -2163,7 +2162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>100</v>
       </c>
@@ -2213,7 +2212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
         <v>100</v>
       </c>
@@ -2263,7 +2262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>100</v>
       </c>
@@ -2313,7 +2312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
         <v>100</v>
       </c>
@@ -2363,7 +2362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>100</v>
       </c>
@@ -2413,7 +2412,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
         <v>100</v>
       </c>
@@ -2463,7 +2462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>100</v>
       </c>
@@ -2513,7 +2512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
         <v>100</v>
       </c>
@@ -2563,7 +2562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>100</v>
       </c>
@@ -2613,7 +2612,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
         <v>100</v>
       </c>
@@ -2663,7 +2662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>100</v>
       </c>
@@ -2713,7 +2712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
         <v>100</v>
       </c>
@@ -2763,7 +2762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>100</v>
       </c>
@@ -2813,7 +2812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>100</v>
       </c>
@@ -2863,7 +2862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>100</v>
       </c>
@@ -2913,7 +2912,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
         <v>100</v>
       </c>
@@ -2961,7 +2960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>100</v>
       </c>
@@ -3009,7 +3008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
         <v>100</v>
       </c>
@@ -3057,7 +3056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>100</v>
       </c>
@@ -3105,7 +3104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
         <v>100</v>
       </c>
@@ -3153,7 +3152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>100</v>
       </c>
@@ -3201,7 +3200,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
         <v>100</v>
       </c>
@@ -3249,7 +3248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>100</v>
       </c>
@@ -3297,7 +3296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
         <v>100</v>
       </c>
@@ -3345,7 +3344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>100</v>
       </c>
@@ -3393,7 +3392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
         <v>100</v>
       </c>
@@ -3441,7 +3440,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>100</v>
       </c>
@@ -3489,7 +3488,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
         <v>100</v>
       </c>
@@ -3537,7 +3536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>100</v>
       </c>
@@ -3585,7 +3584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
         <v>100</v>
       </c>
@@ -3633,7 +3632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>100</v>
       </c>
@@ -3681,7 +3680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
         <v>100</v>
       </c>
@@ -3729,7 +3728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
         <v>100</v>
       </c>
@@ -3777,7 +3776,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
         <v>100</v>
       </c>
@@ -3825,7 +3824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>100</v>
       </c>
@@ -3873,7 +3872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
         <v>100</v>
       </c>
@@ -3921,7 +3920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
         <v>100</v>
       </c>
@@ -3969,7 +3968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
         <v>100</v>
       </c>
@@ -4017,7 +4016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>100</v>
       </c>
@@ -4065,7 +4064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" s="9" t="s">
         <v>100</v>
       </c>
@@ -4113,7 +4112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>100</v>
       </c>
@@ -4161,7 +4160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
         <v>100</v>
       </c>
@@ -4209,7 +4208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>100</v>
       </c>
@@ -4257,7 +4256,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
         <v>100</v>
       </c>
@@ -4305,7 +4304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
         <v>100</v>
       </c>
@@ -4353,7 +4352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
         <v>100</v>
       </c>
@@ -4401,7 +4400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72" s="6" t="s">
         <v>100</v>
       </c>
@@ -4449,7 +4448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73" s="9" t="s">
         <v>100</v>
       </c>
@@ -4497,7 +4496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
         <v>100</v>
       </c>
@@ -4545,7 +4544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75" s="9" t="s">
         <v>100</v>
       </c>
@@ -4593,7 +4592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76" s="6" t="s">
         <v>100</v>
       </c>
@@ -4641,7 +4640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77" s="9" t="s">
         <v>100</v>
       </c>
@@ -4689,7 +4688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>100</v>
       </c>
@@ -4737,7 +4736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79" s="9" t="s">
         <v>100</v>
       </c>
@@ -4785,7 +4784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
         <v>100</v>
       </c>
@@ -4833,7 +4832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81" s="9" t="s">
         <v>100</v>
       </c>
@@ -4881,7 +4880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
         <v>100</v>
       </c>
@@ -4929,7 +4928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83" s="9" t="s">
         <v>100</v>
       </c>
@@ -4977,7 +4976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84" s="6" t="s">
         <v>100</v>
       </c>
@@ -5025,7 +5024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85" s="9" t="s">
         <v>100</v>
       </c>
@@ -5073,7 +5072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
         <v>100</v>
       </c>
@@ -5121,7 +5120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87" s="9" t="s">
         <v>100</v>
       </c>
@@ -5169,7 +5168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
         <v>100</v>
       </c>
@@ -5217,7 +5216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89" s="9" t="s">
         <v>100</v>
       </c>
@@ -5265,7 +5264,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
         <v>100</v>
       </c>
@@ -5313,7 +5312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91" s="9" t="s">
         <v>100</v>
       </c>
@@ -5361,7 +5360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92" s="6" t="s">
         <v>100</v>
       </c>
@@ -5409,7 +5408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A93" s="9" t="s">
         <v>100</v>
       </c>
@@ -5457,7 +5456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94" s="6" t="s">
         <v>100</v>
       </c>
@@ -5505,7 +5504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" s="9" t="s">
         <v>100</v>
       </c>
@@ -5553,7 +5552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96" s="6" t="s">
         <v>100</v>
       </c>
@@ -5601,7 +5600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97" s="9" t="s">
         <v>100</v>
       </c>
@@ -5649,7 +5648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98" s="6" t="s">
         <v>100</v>
       </c>
@@ -5697,7 +5696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99" s="9" t="s">
         <v>100</v>
       </c>
@@ -5745,7 +5744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A100" s="6" t="s">
         <v>100</v>
       </c>
@@ -5793,7 +5792,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101" s="9" t="s">
         <v>100</v>
       </c>
@@ -5841,7 +5840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A102" s="6" t="s">
         <v>100</v>
       </c>
@@ -5889,7 +5888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" s="9" t="s">
         <v>100</v>
       </c>
@@ -5937,7 +5936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104" s="6" t="s">
         <v>100</v>
       </c>
@@ -5985,7 +5984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A105" s="9" t="s">
         <v>100</v>
       </c>
@@ -6033,7 +6032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106" s="6" t="s">
         <v>100</v>
       </c>
@@ -6081,7 +6080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107" s="9" t="s">
         <v>100</v>
       </c>
@@ -6129,7 +6128,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" s="6" t="s">
         <v>100</v>
       </c>
@@ -6177,7 +6176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A109" s="9" t="s">
         <v>100</v>
       </c>
@@ -6225,7 +6224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A110" s="6" t="s">
         <v>100</v>
       </c>
@@ -6273,7 +6272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A111" s="9" t="s">
         <v>100</v>
       </c>
@@ -6321,7 +6320,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A112" s="6" t="s">
         <v>100</v>
       </c>
@@ -6369,7 +6368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A113" s="9" t="s">
         <v>100</v>
       </c>
@@ -6417,7 +6416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A114" s="6" t="s">
         <v>100</v>
       </c>
@@ -6465,7 +6464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A115" s="9" t="s">
         <v>100</v>
       </c>
@@ -6513,7 +6512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A116" s="6" t="s">
         <v>100</v>
       </c>
@@ -6561,7 +6560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117" s="9" t="s">
         <v>100</v>
       </c>
@@ -6609,7 +6608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A118" s="6" t="s">
         <v>100</v>
       </c>
@@ -6657,7 +6656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A119" s="9" t="s">
         <v>100</v>
       </c>
@@ -6705,7 +6704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A120" s="6" t="s">
         <v>100</v>
       </c>
@@ -6753,7 +6752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A121" s="9" t="s">
         <v>100</v>
       </c>
@@ -6801,7 +6800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A122" s="6" t="s">
         <v>100</v>
       </c>
@@ -6849,7 +6848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A123" s="9" t="s">
         <v>100</v>
       </c>
@@ -6897,7 +6896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A124" s="6" t="s">
         <v>100</v>
       </c>
@@ -6945,7 +6944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A125" s="9" t="s">
         <v>100</v>
       </c>
@@ -6993,7 +6992,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A126" s="6" t="s">
         <v>100</v>
       </c>
@@ -7041,7 +7040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A127" s="9" t="s">
         <v>100</v>
       </c>
@@ -7089,7 +7088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A128" s="6" t="s">
         <v>100</v>
       </c>
@@ -7137,7 +7136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A129" s="9" t="s">
         <v>100</v>
       </c>
@@ -7185,7 +7184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A130" s="6" t="s">
         <v>100</v>
       </c>
@@ -7233,7 +7232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A131" s="9" t="s">
         <v>100</v>
       </c>
@@ -7281,7 +7280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A132" s="6" t="s">
         <v>100</v>
       </c>
@@ -7329,7 +7328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A133" s="9" t="s">
         <v>100</v>
       </c>
@@ -7377,7 +7376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A134" s="6" t="s">
         <v>100</v>
       </c>
@@ -7425,7 +7424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A135" s="9" t="s">
         <v>100</v>
       </c>
@@ -7473,7 +7472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A136" s="6" t="s">
         <v>100</v>
       </c>
@@ -7521,7 +7520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A137" s="9" t="s">
         <v>100</v>
       </c>
@@ -7569,7 +7568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A138" s="6" t="s">
         <v>100</v>
       </c>
@@ -7617,7 +7616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A139" s="9" t="s">
         <v>100</v>
       </c>
@@ -7665,7 +7664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A140" s="6" t="s">
         <v>100</v>
       </c>
@@ -7713,7 +7712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A141" s="9" t="s">
         <v>100</v>
       </c>
@@ -7761,7 +7760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A142" s="6" t="s">
         <v>100</v>
       </c>
@@ -7809,7 +7808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A143" s="9" t="s">
         <v>100</v>
       </c>
@@ -7857,7 +7856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A144" s="6" t="s">
         <v>100</v>
       </c>
@@ -7905,7 +7904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145" s="9" t="s">
         <v>100</v>
       </c>
@@ -7953,7 +7952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146" s="6" t="s">
         <v>100</v>
       </c>
@@ -8001,7 +8000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147" s="9" t="s">
         <v>100</v>
       </c>
@@ -8049,7 +8048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148" s="6" t="s">
         <v>100</v>
       </c>
@@ -8097,7 +8096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149" s="9" t="s">
         <v>100</v>
       </c>
@@ -8145,7 +8144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150" s="6" t="s">
         <v>100</v>
       </c>
@@ -8193,7 +8192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A151" s="9" t="s">
         <v>100</v>
       </c>
@@ -8241,7 +8240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A152" s="6" t="s">
         <v>100</v>
       </c>
@@ -8289,7 +8288,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153" s="9" t="s">
         <v>100</v>
       </c>
@@ -8337,7 +8336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154" s="6" t="s">
         <v>100</v>
       </c>
@@ -8385,7 +8384,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155" s="9" t="s">
         <v>100</v>
       </c>
@@ -8433,7 +8432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156" s="6" t="s">
         <v>100</v>
       </c>
@@ -8481,7 +8480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157" s="9" t="s">
         <v>100</v>
       </c>
@@ -8529,7 +8528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158" s="6" t="s">
         <v>100</v>
       </c>
@@ -8577,7 +8576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159" s="9" t="s">
         <v>100</v>
       </c>
@@ -8625,7 +8624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A160" s="6" t="s">
         <v>100</v>
       </c>
@@ -8673,7 +8672,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161" s="9" t="s">
         <v>100</v>
       </c>
@@ -8721,7 +8720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162" s="6" t="s">
         <v>100</v>
       </c>
@@ -8769,7 +8768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A163" s="9" t="s">
         <v>100</v>
       </c>
@@ -8817,7 +8816,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164" s="6" t="s">
         <v>100</v>
       </c>
@@ -8865,7 +8864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165" s="9" t="s">
         <v>100</v>
       </c>
@@ -8913,7 +8912,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166" s="6" t="s">
         <v>100</v>
       </c>
@@ -8961,7 +8960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167" s="9" t="s">
         <v>100</v>
       </c>
@@ -9009,7 +9008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168" s="6" t="s">
         <v>100</v>
       </c>
@@ -9057,7 +9056,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169" s="9" t="s">
         <v>100</v>
       </c>
@@ -9105,7 +9104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170" s="6" t="s">
         <v>100</v>
       </c>
@@ -9153,7 +9152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171" s="9" t="s">
         <v>100</v>
       </c>
@@ -9201,7 +9200,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172" s="6" t="s">
         <v>100</v>
       </c>
@@ -9249,7 +9248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173" s="9" t="s">
         <v>100</v>
       </c>
@@ -9297,7 +9296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174" s="6" t="s">
         <v>100</v>
       </c>
@@ -9345,7 +9344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175" s="9" t="s">
         <v>100</v>
       </c>
@@ -9393,7 +9392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176" s="6" t="s">
         <v>100</v>
       </c>
@@ -9441,7 +9440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A177" s="9" t="s">
         <v>100</v>
       </c>
@@ -9489,7 +9488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A178" s="6" t="s">
         <v>100</v>
       </c>
@@ -9537,7 +9536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A179" s="9" t="s">
         <v>100</v>
       </c>
@@ -9585,7 +9584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A180" s="6" t="s">
         <v>100</v>
       </c>
@@ -9633,7 +9632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A181" s="9" t="s">
         <v>100</v>
       </c>
@@ -9681,7 +9680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A182" s="6" t="s">
         <v>100</v>
       </c>
@@ -9729,7 +9728,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A183" s="9" t="s">
         <v>100</v>
       </c>
@@ -9777,7 +9776,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A184" s="6" t="s">
         <v>100</v>
       </c>
@@ -9825,7 +9824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A185" s="9" t="s">
         <v>100</v>
       </c>
@@ -9873,7 +9872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186" s="6" t="s">
         <v>100</v>
       </c>
@@ -9921,7 +9920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187" s="9" t="s">
         <v>100</v>
       </c>
@@ -9969,7 +9968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A188" s="6" t="s">
         <v>100</v>
       </c>
@@ -10017,7 +10016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
         <v>100</v>
       </c>
@@ -10065,7 +10064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A190" s="6" t="s">
         <v>100</v>
       </c>
@@ -10113,7 +10112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
         <v>100</v>
       </c>
@@ -10161,7 +10160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A192" s="6" t="s">
         <v>100</v>
       </c>
@@ -10209,7 +10208,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
         <v>100</v>
       </c>
@@ -10257,7 +10256,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A194" s="6" t="s">
         <v>100</v>
       </c>
@@ -10305,7 +10304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A195" s="9" t="s">
         <v>100</v>
       </c>
@@ -10353,7 +10352,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A196" s="6" t="s">
         <v>100</v>
       </c>
@@ -10401,7 +10400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A197" s="9" t="s">
         <v>100</v>
       </c>
@@ -10449,7 +10448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A198" s="6" t="s">
         <v>100</v>
       </c>
@@ -10497,7 +10496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A199" s="9" t="s">
         <v>100</v>
       </c>
@@ -10545,7 +10544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A200" s="6" t="s">
         <v>100</v>
       </c>
@@ -10593,7 +10592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
         <v>100</v>
       </c>
@@ -10641,7 +10640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A202" s="6" t="s">
         <v>100</v>
       </c>
@@ -10689,7 +10688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A203" s="9" t="s">
         <v>100</v>
       </c>
@@ -10737,7 +10736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A204" s="6" t="s">
         <v>100</v>
       </c>
@@ -10785,7 +10784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A205" s="9" t="s">
         <v>100</v>
       </c>
@@ -10833,7 +10832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A206" s="6" t="s">
         <v>100</v>
       </c>
@@ -10881,7 +10880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A207" s="9" t="s">
         <v>100</v>
       </c>
@@ -10929,7 +10928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A208" s="6" t="s">
         <v>100</v>
       </c>
@@ -10977,7 +10976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
         <v>100</v>
       </c>
@@ -11025,7 +11024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A210" s="6" t="s">
         <v>100</v>
       </c>
@@ -11073,7 +11072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A211" s="9" t="s">
         <v>100</v>
       </c>
@@ -11121,7 +11120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A212" s="6" t="s">
         <v>100</v>
       </c>
@@ -11169,7 +11168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A213" s="9" t="s">
         <v>100</v>
       </c>
@@ -11217,7 +11216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A214" s="6" t="s">
         <v>100</v>
       </c>
@@ -11265,7 +11264,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A215" s="9" t="s">
         <v>100</v>
       </c>
@@ -11313,7 +11312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A216" s="6" t="s">
         <v>100</v>
       </c>
@@ -11361,7 +11360,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
         <v>100</v>
       </c>
@@ -11409,7 +11408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A218" s="6" t="s">
         <v>100</v>
       </c>
@@ -11457,7 +11456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
         <v>100</v>
       </c>
@@ -11505,7 +11504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A220" s="6" t="s">
         <v>100</v>
       </c>
@@ -11553,7 +11552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
         <v>100</v>
       </c>
@@ -11601,7 +11600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A222" s="6" t="s">
         <v>100</v>
       </c>
@@ -11649,7 +11648,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A223" s="9" t="s">
         <v>100</v>
       </c>
@@ -11697,7 +11696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A224" s="6" t="s">
         <v>100</v>
       </c>
@@ -11745,7 +11744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A225" s="9" t="s">
         <v>100</v>
       </c>
@@ -11793,7 +11792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A226" s="6" t="s">
         <v>100</v>
       </c>
@@ -11841,7 +11840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A227" s="9" t="s">
         <v>100</v>
       </c>
@@ -11889,7 +11888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A228" s="6" t="s">
         <v>100</v>
       </c>
@@ -11937,7 +11936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A229" s="9" t="s">
         <v>100</v>
       </c>
@@ -11985,7 +11984,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A230" s="6" t="s">
         <v>100</v>
       </c>
@@ -12033,7 +12032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A231" s="9" t="s">
         <v>100</v>
       </c>
@@ -12081,7 +12080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A232" s="6" t="s">
         <v>100</v>
       </c>
@@ -12129,7 +12128,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A233" s="9" t="s">
         <v>100</v>
       </c>
@@ -12177,7 +12176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A234" s="6" t="s">
         <v>100</v>
       </c>
@@ -12225,7 +12224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A235" s="9" t="s">
         <v>100</v>
       </c>
@@ -12273,7 +12272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A236" s="6" t="s">
         <v>100</v>
       </c>
@@ -12321,7 +12320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A237" s="9" t="s">
         <v>100</v>
       </c>
@@ -12369,7 +12368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A238" s="6" t="s">
         <v>100</v>
       </c>
@@ -12417,7 +12416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A239" s="9" t="s">
         <v>100</v>
       </c>
@@ -12465,7 +12464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A240" s="6" t="s">
         <v>100</v>
       </c>
@@ -12513,7 +12512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A241" s="9" t="s">
         <v>100</v>
       </c>
@@ -12561,7 +12560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="242" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A242" s="6" t="s">
         <v>100</v>
       </c>
@@ -12609,7 +12608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A243" s="9" t="s">
         <v>100</v>
       </c>
@@ -12657,7 +12656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="244" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A244" s="6" t="s">
         <v>100</v>
       </c>
@@ -12705,7 +12704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A245" s="9" t="s">
         <v>100</v>
       </c>
@@ -12753,7 +12752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A246" s="6" t="s">
         <v>100</v>
       </c>
@@ -12801,7 +12800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A247" s="9" t="s">
         <v>100</v>
       </c>
@@ -12849,7 +12848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A248" s="6" t="s">
         <v>100</v>
       </c>
@@ -12897,7 +12896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A249" s="9" t="s">
         <v>100</v>
       </c>
@@ -12945,7 +12944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A250" s="6" t="s">
         <v>100</v>
       </c>
@@ -12993,7 +12992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A251" s="9" t="s">
         <v>100</v>
       </c>
@@ -13041,7 +13040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A252" s="6" t="s">
         <v>100</v>
       </c>
@@ -13089,7 +13088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A253" s="9" t="s">
         <v>100</v>
       </c>
@@ -13137,7 +13136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A254" s="6" t="s">
         <v>100</v>
       </c>
@@ -13185,7 +13184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A255" s="9" t="s">
         <v>100</v>
       </c>
@@ -13233,7 +13232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A256" s="6" t="s">
         <v>100</v>
       </c>
@@ -13281,7 +13280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A257" s="9" t="s">
         <v>100</v>
       </c>
@@ -13329,7 +13328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A258" s="6" t="s">
         <v>100</v>
       </c>
@@ -13377,7 +13376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A259" s="9" t="s">
         <v>100</v>
       </c>
@@ -13425,7 +13424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A260" s="6" t="s">
         <v>100</v>
       </c>
@@ -13473,7 +13472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A261" s="9" t="s">
         <v>100</v>
       </c>
@@ -13521,7 +13520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A262" s="6" t="s">
         <v>100</v>
       </c>
@@ -13569,7 +13568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A263" s="9" t="s">
         <v>100</v>
       </c>
@@ -13617,7 +13616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A264" s="6" t="s">
         <v>100</v>
       </c>
@@ -13665,7 +13664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A265" s="9" t="s">
         <v>100</v>
       </c>
@@ -13713,7 +13712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A266" s="6" t="s">
         <v>100</v>
       </c>
@@ -13761,7 +13760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A267" s="9" t="s">
         <v>100</v>
       </c>
@@ -13809,7 +13808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A268" s="6" t="s">
         <v>100</v>
       </c>
@@ -13857,7 +13856,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A269" s="9" t="s">
         <v>100</v>
       </c>
@@ -13905,7 +13904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A270" s="6" t="s">
         <v>100</v>
       </c>
@@ -13953,7 +13952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="271" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A271" s="9" t="s">
         <v>100</v>
       </c>
@@ -14001,7 +14000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A272" s="6" t="s">
         <v>100</v>
       </c>
@@ -14049,7 +14048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="273" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A273" s="9" t="s">
         <v>100</v>
       </c>
@@ -14097,7 +14096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A274" s="6" t="s">
         <v>100</v>
       </c>
@@ -14145,7 +14144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A275" s="9" t="s">
         <v>100</v>
       </c>
@@ -14193,7 +14192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A276" s="6" t="s">
         <v>100</v>
       </c>
@@ -14241,7 +14240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A277" s="9" t="s">
         <v>100</v>
       </c>
@@ -14289,7 +14288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="278" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A278" s="6" t="s">
         <v>100</v>
       </c>
@@ -14337,7 +14336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A279" s="9" t="s">
         <v>100</v>
       </c>
@@ -14385,7 +14384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A280" s="6" t="s">
         <v>100</v>
       </c>
@@ -14433,7 +14432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A281" s="6" t="s">
         <v>100</v>
       </c>
@@ -14481,7 +14480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A282" s="9" t="s">
         <v>100</v>
       </c>
@@ -14529,7 +14528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A283" s="6" t="s">
         <v>100</v>
       </c>
@@ -14577,7 +14576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A284" s="9" t="s">
         <v>100</v>
       </c>
@@ -14625,7 +14624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A285" s="6" t="s">
         <v>100</v>
       </c>
@@ -14673,7 +14672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A286" s="9" t="s">
         <v>100</v>
       </c>
@@ -14721,7 +14720,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A287" s="6" t="s">
         <v>100</v>
       </c>
@@ -14769,7 +14768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A288" s="9" t="s">
         <v>100</v>
       </c>
@@ -14817,7 +14816,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A289" s="6" t="s">
         <v>100</v>
       </c>
@@ -14865,7 +14864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A290" s="9" t="s">
         <v>100</v>
       </c>
@@ -14913,7 +14912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A291" s="6" t="s">
         <v>100</v>
       </c>
@@ -14961,7 +14960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A292" s="9" t="s">
         <v>100</v>
       </c>
@@ -15009,7 +15008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A293" s="6" t="s">
         <v>100</v>
       </c>
@@ -15057,7 +15056,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A294" s="9" t="s">
         <v>100</v>
       </c>
@@ -15105,7 +15104,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="295" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A295" s="6" t="s">
         <v>100</v>
       </c>
@@ -15153,7 +15152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A296" s="9" t="s">
         <v>100</v>
       </c>
@@ -15201,7 +15200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A297" s="6" t="s">
         <v>100</v>
       </c>
@@ -15249,7 +15248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A298" s="9" t="s">
         <v>100</v>
       </c>
@@ -15297,7 +15296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="299" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A299" s="6" t="s">
         <v>100</v>
       </c>
@@ -15345,7 +15344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="300" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A300" s="9" t="s">
         <v>100</v>
       </c>
@@ -15393,7 +15392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A301" s="6" t="s">
         <v>100</v>
       </c>
@@ -15441,7 +15440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A302" s="9" t="s">
         <v>100</v>
       </c>
@@ -15489,7 +15488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A303" s="6" t="s">
         <v>100</v>
       </c>
@@ -15537,7 +15536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="304" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A304" s="9" t="s">
         <v>100</v>
       </c>
@@ -15585,7 +15584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A305" s="6" t="s">
         <v>100</v>
       </c>
@@ -15633,7 +15632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A306" s="9" t="s">
         <v>100</v>
       </c>
@@ -15681,7 +15680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A307" s="6" t="s">
         <v>100</v>
       </c>
@@ -15729,7 +15728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A308" s="9" t="s">
         <v>100</v>
       </c>
@@ -15777,7 +15776,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A309" s="6" t="s">
         <v>100</v>
       </c>
@@ -15825,7 +15824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A310" s="9" t="s">
         <v>100</v>
       </c>
@@ -15873,7 +15872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A311" s="6" t="s">
         <v>100</v>
       </c>
@@ -15921,7 +15920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A312" s="9" t="s">
         <v>100</v>
       </c>
@@ -15969,7 +15968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A313" s="6" t="s">
         <v>100</v>
       </c>
@@ -16017,7 +16016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A314" s="9" t="s">
         <v>100</v>
       </c>
@@ -16065,7 +16064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A315" s="6" t="s">
         <v>100</v>
       </c>
@@ -16113,7 +16112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="316" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A316" s="9" t="s">
         <v>100</v>
       </c>
@@ -16161,7 +16160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A317" s="6" t="s">
         <v>100</v>
       </c>
@@ -16209,7 +16208,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A318" s="9" t="s">
         <v>100</v>
       </c>
@@ -16257,7 +16256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A319" s="6" t="s">
         <v>100</v>
       </c>
@@ -16305,7 +16304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A320" s="9" t="s">
         <v>100</v>
       </c>
@@ -16353,7 +16352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A321" s="6" t="s">
         <v>100</v>
       </c>
@@ -16401,7 +16400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A322" s="9" t="s">
         <v>100</v>
       </c>
@@ -16449,7 +16448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A323" s="6" t="s">
         <v>100</v>
       </c>
@@ -16497,7 +16496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="324" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A324" s="9" t="s">
         <v>100</v>
       </c>
@@ -16545,7 +16544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A325" s="6" t="s">
         <v>100</v>
       </c>
@@ -16593,7 +16592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A326" s="9" t="s">
         <v>100</v>
       </c>
@@ -16641,7 +16640,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A327" s="6" t="s">
         <v>100</v>
       </c>
@@ -16689,7 +16688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A328" s="9" t="s">
         <v>100</v>
       </c>
@@ -16737,7 +16736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A329" s="6" t="s">
         <v>100</v>
       </c>
@@ -16785,7 +16784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A330" s="9" t="s">
         <v>100</v>
       </c>
@@ -16833,7 +16832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A331" s="6" t="s">
         <v>100</v>
       </c>
@@ -16881,7 +16880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A332" s="9" t="s">
         <v>100</v>
       </c>
@@ -16929,7 +16928,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A333" s="6" t="s">
         <v>100</v>
       </c>
@@ -16977,7 +16976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A334" s="9" t="s">
         <v>100</v>
       </c>
@@ -17025,7 +17024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A335" s="6" t="s">
         <v>100</v>
       </c>
@@ -17073,7 +17072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A336" s="9" t="s">
         <v>100</v>
       </c>
@@ -17121,7 +17120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="337" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A337" s="6" t="s">
         <v>100</v>
       </c>
@@ -17169,7 +17168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="338" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A338" s="9" t="s">
         <v>100</v>
       </c>
@@ -17217,7 +17216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="339" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A339" s="6" t="s">
         <v>100</v>
       </c>
@@ -17265,7 +17264,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A340" s="9" t="s">
         <v>100</v>
       </c>
@@ -17313,7 +17312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A341" s="6" t="s">
         <v>100</v>
       </c>
@@ -17361,7 +17360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A342" s="9" t="s">
         <v>100</v>
       </c>
@@ -17409,7 +17408,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A343" s="6" t="s">
         <v>100</v>
       </c>
@@ -17457,7 +17456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A344" s="9" t="s">
         <v>100</v>
       </c>
@@ -17505,7 +17504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="345" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A345" s="6" t="s">
         <v>100</v>
       </c>
@@ -17553,7 +17552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="346" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A346" s="9" t="s">
         <v>100</v>
       </c>
@@ -17601,7 +17600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="347" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A347" s="6" t="s">
         <v>100</v>
       </c>
@@ -17649,7 +17648,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="348" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A348" s="9" t="s">
         <v>100</v>
       </c>
@@ -17697,7 +17696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="349" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A349" s="6" t="s">
         <v>100</v>
       </c>
@@ -17745,7 +17744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="350" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A350" s="9" t="s">
         <v>100</v>
       </c>
@@ -17793,7 +17792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A351" s="6" t="s">
         <v>100</v>
       </c>
@@ -17841,7 +17840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A352" s="9" t="s">
         <v>100</v>
       </c>
@@ -17889,7 +17888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A353" s="6" t="s">
         <v>100</v>
       </c>
@@ -17937,7 +17936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A354" s="9" t="s">
         <v>100</v>
       </c>
@@ -17985,7 +17984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A355" s="6" t="s">
         <v>100</v>
       </c>
@@ -18033,7 +18032,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A356" s="9" t="s">
         <v>100</v>
       </c>
@@ -18081,7 +18080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A357" s="6" t="s">
         <v>100</v>
       </c>
@@ -18129,7 +18128,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A358" s="9" t="s">
         <v>100</v>
       </c>
@@ -18177,7 +18176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A359" s="6" t="s">
         <v>100</v>
       </c>
@@ -18225,7 +18224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A360" s="9" t="s">
         <v>100</v>
       </c>
@@ -18273,7 +18272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A361" s="6" t="s">
         <v>100</v>
       </c>
@@ -18321,7 +18320,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A362" s="9" t="s">
         <v>100</v>
       </c>
@@ -18369,7 +18368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A363" s="6" t="s">
         <v>100</v>
       </c>
@@ -18417,7 +18416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A364" s="9" t="s">
         <v>100</v>
       </c>
@@ -18465,7 +18464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A365" s="6" t="s">
         <v>100</v>
       </c>
@@ -18513,7 +18512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A366" s="9" t="s">
         <v>100</v>
       </c>
@@ -18561,7 +18560,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A367" s="6" t="s">
         <v>100</v>
       </c>
@@ -18609,7 +18608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A368" s="9" t="s">
         <v>100</v>
       </c>
@@ -18657,7 +18656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A369" s="6" t="s">
         <v>100</v>
       </c>
@@ -18705,7 +18704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A370" s="9" t="s">
         <v>100</v>
       </c>
@@ -18753,7 +18752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="371" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A371" s="6" t="s">
         <v>100</v>
       </c>
@@ -18801,7 +18800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A372" s="9" t="s">
         <v>100</v>
       </c>
@@ -18849,7 +18848,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="373" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A373" s="6" t="s">
         <v>100</v>
       </c>
@@ -18897,7 +18896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A374" s="9" t="s">
         <v>100</v>
       </c>
@@ -18945,7 +18944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="375" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A375" s="6" t="s">
         <v>100</v>
       </c>
@@ -18993,7 +18992,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A376" s="9" t="s">
         <v>100</v>
       </c>
@@ -19041,7 +19040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A377" s="6" t="s">
         <v>100</v>
       </c>
@@ -19089,7 +19088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A378" s="9" t="s">
         <v>100</v>
       </c>
@@ -19137,7 +19136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A379" s="6" t="s">
         <v>100</v>
       </c>
@@ -19185,7 +19184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A380" s="9" t="s">
         <v>100</v>
       </c>
@@ -19233,7 +19232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A381" s="6" t="s">
         <v>100</v>
       </c>
@@ -19281,7 +19280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A382" s="9" t="s">
         <v>100</v>
       </c>
@@ -19329,7 +19328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A383" s="6" t="s">
         <v>100</v>
       </c>
@@ -19377,7 +19376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A384" s="9" t="s">
         <v>100</v>
       </c>
@@ -19425,7 +19424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="385" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A385" s="6" t="s">
         <v>100</v>
       </c>
@@ -19473,7 +19472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A386" s="9" t="s">
         <v>100</v>
       </c>
@@ -19521,7 +19520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="387" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A387" s="6" t="s">
         <v>100</v>
       </c>
@@ -19569,7 +19568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A388" s="9" t="s">
         <v>100</v>
       </c>
@@ -19617,7 +19616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A389" s="6" t="s">
         <v>100</v>
       </c>
@@ -19665,7 +19664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A390" s="9" t="s">
         <v>100</v>
       </c>
@@ -19713,7 +19712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A391" s="6" t="s">
         <v>100</v>
       </c>
@@ -19761,7 +19760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="392" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A392" s="9" t="s">
         <v>100</v>
       </c>
@@ -19809,7 +19808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A393" s="6" t="s">
         <v>100</v>
       </c>
@@ -19857,7 +19856,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A394" s="9" t="s">
         <v>100</v>
       </c>
@@ -19905,7 +19904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A395" s="6" t="s">
         <v>100</v>
       </c>
@@ -19953,7 +19952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A396" s="9" t="s">
         <v>100</v>
       </c>
@@ -20001,7 +20000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="397" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A397" s="6" t="s">
         <v>100</v>
       </c>
@@ -20049,7 +20048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="398" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A398" s="9" t="s">
         <v>100</v>
       </c>
@@ -20097,7 +20096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A399" s="6" t="s">
         <v>100</v>
       </c>
@@ -20145,7 +20144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A400" s="9" t="s">
         <v>100</v>
       </c>
@@ -20193,7 +20192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A401" s="6" t="s">
         <v>100</v>
       </c>
@@ -20241,7 +20240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A402" s="9" t="s">
         <v>100</v>
       </c>
@@ -20289,7 +20288,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A403" s="6" t="s">
         <v>100</v>
       </c>
@@ -20337,7 +20336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A404" s="9" t="s">
         <v>100</v>
       </c>
@@ -20385,7 +20384,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A405" s="6" t="s">
         <v>100</v>
       </c>
@@ -20433,7 +20432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A406" s="9" t="s">
         <v>100</v>
       </c>
@@ -20481,7 +20480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A407" s="6" t="s">
         <v>100</v>
       </c>
@@ -20529,7 +20528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="408" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A408" s="9" t="s">
         <v>100</v>
       </c>
@@ -20577,7 +20576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A409" s="6" t="s">
         <v>100</v>
       </c>
@@ -20625,7 +20624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A410" s="9" t="s">
         <v>100</v>
       </c>
@@ -20673,7 +20672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A411" s="6" t="s">
         <v>100</v>
       </c>
@@ -20721,7 +20720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A412" s="9" t="s">
         <v>100</v>
       </c>
@@ -20769,7 +20768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A413" s="6" t="s">
         <v>100</v>
       </c>
@@ -20817,7 +20816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A414" s="9" t="s">
         <v>100</v>
       </c>
@@ -20865,7 +20864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A415" s="6" t="s">
         <v>100</v>
       </c>
@@ -20913,7 +20912,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A416" s="9" t="s">
         <v>100</v>
       </c>
@@ -20961,7 +20960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A417" s="6" t="s">
         <v>100</v>
       </c>
@@ -21009,7 +21008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A418" s="9" t="s">
         <v>100</v>
       </c>
@@ -21057,7 +21056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A419" s="6" t="s">
         <v>100</v>
       </c>
@@ -21105,7 +21104,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A420" s="9" t="s">
         <v>100</v>
       </c>
@@ -21153,7 +21152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A421" s="6" t="s">
         <v>100</v>
       </c>
@@ -21201,7 +21200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A422" s="9" t="s">
         <v>100</v>
       </c>
@@ -21249,7 +21248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A423" s="6" t="s">
         <v>100</v>
       </c>
@@ -21297,7 +21296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="424" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A424" s="9" t="s">
         <v>100</v>
       </c>
@@ -21345,7 +21344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="425" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A425" s="6" t="s">
         <v>100</v>
       </c>
@@ -21393,7 +21392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="426" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A426" s="9" t="s">
         <v>100</v>
       </c>
@@ -21441,7 +21440,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="427" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A427" s="6" t="s">
         <v>100</v>
       </c>
@@ -21489,7 +21488,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="428" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A428" s="9" t="s">
         <v>100</v>
       </c>
@@ -21537,7 +21536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="429" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A429" s="6" t="s">
         <v>100</v>
       </c>
@@ -21585,7 +21584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="430" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A430" s="9" t="s">
         <v>100</v>
       </c>
@@ -21633,7 +21632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="431" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A431" s="6" t="s">
         <v>100</v>
       </c>
@@ -21681,7 +21680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A432" s="9" t="s">
         <v>100</v>
       </c>
@@ -21729,7 +21728,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A433" s="6" t="s">
         <v>100</v>
       </c>
@@ -21777,7 +21776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A434" s="9" t="s">
         <v>100</v>
       </c>
@@ -21825,7 +21824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A435" s="6" t="s">
         <v>100</v>
       </c>
@@ -21873,7 +21872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="436" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A436" s="9" t="s">
         <v>100</v>
       </c>
@@ -21921,7 +21920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A437" s="6" t="s">
         <v>100</v>
       </c>
@@ -21969,7 +21968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="438" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A438" s="9" t="s">
         <v>100</v>
       </c>
@@ -22017,7 +22016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="439" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A439" s="6" t="s">
         <v>100</v>
       </c>
@@ -22065,7 +22064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="440" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A440" s="9" t="s">
         <v>100</v>
       </c>
@@ -22113,7 +22112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="441" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A441" s="6" t="s">
         <v>100</v>
       </c>
@@ -22161,7 +22160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A442" s="9" t="s">
         <v>100</v>
       </c>
@@ -22209,7 +22208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A443" s="6" t="s">
         <v>100</v>
       </c>
@@ -22257,7 +22256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A444" s="9" t="s">
         <v>100</v>
       </c>
@@ -22305,7 +22304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A445" s="6" t="s">
         <v>100</v>
       </c>
@@ -22353,7 +22352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="446" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A446" s="9" t="s">
         <v>100</v>
       </c>
@@ -22401,7 +22400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="447" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A447" s="6" t="s">
         <v>100</v>
       </c>
@@ -22449,7 +22448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="448" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A448" s="9" t="s">
         <v>100</v>
       </c>
@@ -22497,7 +22496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="449" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A449" s="6" t="s">
         <v>100</v>
       </c>
@@ -22545,7 +22544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="450" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A450" s="9" t="s">
         <v>100</v>
       </c>
@@ -22593,7 +22592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="451" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A451" s="6" t="s">
         <v>100</v>
       </c>
@@ -22641,7 +22640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="452" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A452" s="9" t="s">
         <v>100</v>
       </c>
@@ -22689,7 +22688,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="453" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A453" s="6" t="s">
         <v>100</v>
       </c>
@@ -22737,7 +22736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="454" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A454" s="9" t="s">
         <v>100</v>
       </c>
@@ -22785,7 +22784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="455" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A455" s="6" t="s">
         <v>100</v>
       </c>
@@ -22833,7 +22832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="456" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A456" s="9" t="s">
         <v>100</v>
       </c>
@@ -22881,7 +22880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="457" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A457" s="6" t="s">
         <v>100</v>
       </c>
@@ -22929,7 +22928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="458" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A458" s="9" t="s">
         <v>100</v>
       </c>
@@ -22977,7 +22976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="459" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A459" s="6" t="s">
         <v>100</v>
       </c>
@@ -23025,7 +23024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="460" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A460" s="9" t="s">
         <v>100</v>
       </c>
@@ -23073,7 +23072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="461" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A461" s="6" t="s">
         <v>100</v>
       </c>
@@ -23121,7 +23120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="462" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A462" s="9" t="s">
         <v>100</v>
       </c>
@@ -23169,7 +23168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="463" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A463" s="6" t="s">
         <v>100</v>
       </c>
@@ -23217,7 +23216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="464" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A464" s="9" t="s">
         <v>100</v>
       </c>
@@ -23265,7 +23264,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="465" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A465" s="6" t="s">
         <v>100</v>
       </c>
@@ -23313,7 +23312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="466" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A466" s="9" t="s">
         <v>100</v>
       </c>
@@ -23361,7 +23360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="467" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A467" s="6" t="s">
         <v>100</v>
       </c>
@@ -23409,7 +23408,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="468" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A468" s="9" t="s">
         <v>100</v>
       </c>
@@ -23457,7 +23456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="469" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A469" s="6" t="s">
         <v>100</v>
       </c>
@@ -23505,7 +23504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="470" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A470" s="9" t="s">
         <v>100</v>
       </c>
@@ -23553,7 +23552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="471" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A471" s="6" t="s">
         <v>100</v>
       </c>
@@ -23601,7 +23600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="472" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A472" s="9" t="s">
         <v>100</v>
       </c>
@@ -23649,7 +23648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="473" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A473" s="6" t="s">
         <v>100</v>
       </c>
@@ -23697,7 +23696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="474" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A474" s="9" t="s">
         <v>100</v>
       </c>
@@ -23745,7 +23744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="475" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A475" s="6" t="s">
         <v>100</v>
       </c>
@@ -23793,7 +23792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="476" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A476" s="9" t="s">
         <v>100</v>
       </c>
@@ -23841,7 +23840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="477" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A477" s="6" t="s">
         <v>100</v>
       </c>
@@ -23889,7 +23888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="478" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A478" s="9" t="s">
         <v>100</v>
       </c>
@@ -23937,7 +23936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="479" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A479" s="6" t="s">
         <v>100</v>
       </c>
@@ -23985,7 +23984,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="480" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A480" s="9" t="s">
         <v>100</v>
       </c>
@@ -24033,7 +24032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="481" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A481" s="6" t="s">
         <v>100</v>
       </c>
@@ -24081,7 +24080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="482" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A482" s="9" t="s">
         <v>100</v>
       </c>
@@ -24129,7 +24128,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="483" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A483" s="6" t="s">
         <v>100</v>
       </c>
@@ -24177,7 +24176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="484" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A484" s="9" t="s">
         <v>100</v>
       </c>
@@ -24225,7 +24224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="485" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A485" s="6" t="s">
         <v>100</v>
       </c>
@@ -24273,7 +24272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="486" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A486" s="9" t="s">
         <v>100</v>
       </c>
@@ -24321,7 +24320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="487" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A487" s="6" t="s">
         <v>100</v>
       </c>
@@ -24369,7 +24368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="488" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A488" s="9" t="s">
         <v>100</v>
       </c>
@@ -24417,7 +24416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="489" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A489" s="6" t="s">
         <v>100</v>
       </c>
@@ -24465,7 +24464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="490" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A490" s="9" t="s">
         <v>100</v>
       </c>
@@ -24513,7 +24512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="491" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A491" s="6" t="s">
         <v>100</v>
       </c>
@@ -24561,7 +24560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="492" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A492" s="9" t="s">
         <v>100</v>
       </c>
@@ -24609,7 +24608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="493" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A493" s="6" t="s">
         <v>100</v>
       </c>
@@ -24657,7 +24656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="494" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A494" s="9" t="s">
         <v>100</v>
       </c>
@@ -24705,7 +24704,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="495" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A495" s="6" t="s">
         <v>100</v>
       </c>
@@ -24753,7 +24752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="496" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A496" s="9" t="s">
         <v>100</v>
       </c>
@@ -24801,7 +24800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="497" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A497" s="6" t="s">
         <v>100</v>
       </c>
@@ -24849,7 +24848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="498" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A498" s="9" t="s">
         <v>100</v>
       </c>
@@ -24897,7 +24896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="499" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A499" s="6" t="s">
         <v>100</v>
       </c>
@@ -24945,7 +24944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="500" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A500" s="9" t="s">
         <v>100</v>
       </c>
@@ -24993,7 +24992,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="501" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A501" s="6" t="s">
         <v>100</v>
       </c>
@@ -25041,7 +25040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="502" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A502" s="9" t="s">
         <v>100</v>
       </c>
@@ -25089,7 +25088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="503" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A503" s="6" t="s">
         <v>100</v>
       </c>
@@ -25137,7 +25136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="504" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A504" s="9" t="s">
         <v>100</v>
       </c>
@@ -25185,7 +25184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="505" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A505" s="6" t="s">
         <v>100</v>
       </c>
@@ -25233,7 +25232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="506" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A506" s="9" t="s">
         <v>100</v>
       </c>
@@ -25281,7 +25280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="507" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A507" s="6" t="s">
         <v>100</v>
       </c>
@@ -25329,7 +25328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="508" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A508" s="9" t="s">
         <v>100</v>
       </c>
@@ -25377,7 +25376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="509" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A509" s="6" t="s">
         <v>100</v>
       </c>
@@ -25425,7 +25424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="510" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A510" s="9" t="s">
         <v>100</v>
       </c>
@@ -25473,7 +25472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="511" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A511" s="6" t="s">
         <v>100</v>
       </c>
@@ -25521,7 +25520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="512" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A512" s="9" t="s">
         <v>100</v>
       </c>
@@ -25569,7 +25568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="513" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A513" s="6" t="s">
         <v>100</v>
       </c>
@@ -25617,7 +25616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="514" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A514" s="9" t="s">
         <v>100</v>
       </c>
@@ -25665,7 +25664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="515" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A515" s="6" t="s">
         <v>100</v>
       </c>
@@ -25713,7 +25712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="516" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A516" s="9" t="s">
         <v>100</v>
       </c>
@@ -25761,7 +25760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="517" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A517" s="6" t="s">
         <v>100</v>
       </c>
@@ -25809,7 +25808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="518" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A518" s="9" t="s">
         <v>100</v>
       </c>
@@ -25857,7 +25856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="519" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A519" s="6" t="s">
         <v>100</v>
       </c>
@@ -25905,7 +25904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="520" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A520" s="9" t="s">
         <v>100</v>
       </c>
@@ -25953,7 +25952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="521" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A521" s="6" t="s">
         <v>100</v>
       </c>
@@ -26001,7 +26000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="522" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A522" s="9" t="s">
         <v>100</v>
       </c>
@@ -26049,7 +26048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="523" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A523" s="6" t="s">
         <v>100</v>
       </c>
@@ -26097,7 +26096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="524" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A524" s="9" t="s">
         <v>100</v>
       </c>
@@ -26145,7 +26144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="525" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A525" s="6" t="s">
         <v>100</v>
       </c>
@@ -26193,7 +26192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="526" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A526" s="9" t="s">
         <v>100</v>
       </c>
@@ -26241,7 +26240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="527" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A527" s="6" t="s">
         <v>100</v>
       </c>
@@ -26289,7 +26288,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="528" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A528" s="9" t="s">
         <v>100</v>
       </c>
@@ -26337,7 +26336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="529" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A529" s="6" t="s">
         <v>100</v>
       </c>
@@ -26385,7 +26384,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="530" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A530" s="9" t="s">
         <v>100</v>
       </c>
@@ -26433,7 +26432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="531" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A531" s="6" t="s">
         <v>100</v>
       </c>
@@ -26481,7 +26480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="532" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A532" s="9" t="s">
         <v>100</v>
       </c>
@@ -26529,7 +26528,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="533" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A533" s="6" t="s">
         <v>100</v>
       </c>
@@ -26577,7 +26576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="534" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A534" s="9" t="s">
         <v>100</v>
       </c>
@@ -26625,7 +26624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="535" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A535" s="6" t="s">
         <v>100</v>
       </c>
@@ -26673,7 +26672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="536" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A536" s="9" t="s">
         <v>100</v>
       </c>
@@ -26721,7 +26720,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="537" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A537" s="6" t="s">
         <v>100</v>
       </c>
@@ -26769,7 +26768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="538" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A538" s="9" t="s">
         <v>100</v>
       </c>
@@ -26817,7 +26816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="539" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A539" s="6" t="s">
         <v>100</v>
       </c>
@@ -26865,7 +26864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="540" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A540" s="9" t="s">
         <v>100</v>
       </c>
@@ -26913,7 +26912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="541" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A541" s="6" t="s">
         <v>100</v>
       </c>
@@ -26961,7 +26960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="542" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A542" s="9" t="s">
         <v>100</v>
       </c>
@@ -27009,7 +27008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="543" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A543" s="6" t="s">
         <v>100</v>
       </c>
@@ -27057,7 +27056,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="544" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A544" s="9" t="s">
         <v>100</v>
       </c>
@@ -27105,7 +27104,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A545" s="6" t="s">
         <v>100</v>
       </c>
@@ -27153,7 +27152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A546" s="9" t="s">
         <v>100</v>
       </c>
@@ -27201,7 +27200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A547" s="6" t="s">
         <v>100</v>
       </c>
@@ -27249,7 +27248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A548" s="9" t="s">
         <v>100</v>
       </c>
@@ -27297,7 +27296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="549" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A549" s="6" t="s">
         <v>100</v>
       </c>
@@ -27345,7 +27344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A550" s="9" t="s">
         <v>100</v>
       </c>
@@ -27393,7 +27392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="551" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A551" s="6" t="s">
         <v>100</v>
       </c>
@@ -27441,7 +27440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="552" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A552" s="9" t="s">
         <v>100</v>
       </c>
@@ -27489,7 +27488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="553" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A553" s="6" t="s">
         <v>100</v>
       </c>
@@ -27537,7 +27536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="554" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A554" s="9" t="s">
         <v>100</v>
       </c>
@@ -27585,7 +27584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="555" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A555" s="6" t="s">
         <v>100</v>
       </c>
@@ -27633,7 +27632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="556" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A556" s="9" t="s">
         <v>100</v>
       </c>
@@ -27681,7 +27680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="557" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A557" s="6" t="s">
         <v>100</v>
       </c>
@@ -27729,7 +27728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A558" s="9" t="s">
         <v>100</v>
       </c>
@@ -27777,7 +27776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="559" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A559" s="6" t="s">
         <v>100</v>
       </c>
@@ -27825,7 +27824,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="560" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A560" s="9" t="s">
         <v>100</v>
       </c>
@@ -27873,7 +27872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="561" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A561" s="6" t="s">
         <v>100</v>
       </c>
@@ -27921,7 +27920,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A562" s="9" t="s">
         <v>100</v>
       </c>
@@ -27969,7 +27968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A563" s="6" t="s">
         <v>100</v>
       </c>
@@ -28017,7 +28016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A564" s="9" t="s">
         <v>100</v>
       </c>
@@ -28065,7 +28064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A565" s="6" t="s">
         <v>100</v>
       </c>
@@ -28113,7 +28112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="566" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A566" s="9" t="s">
         <v>100</v>
       </c>
@@ -28161,7 +28160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A567" s="6" t="s">
         <v>100</v>
       </c>
@@ -28209,7 +28208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="568" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A568" s="9" t="s">
         <v>100</v>
       </c>
@@ -28257,7 +28256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="569" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A569" s="6" t="s">
         <v>100</v>
       </c>
@@ -28305,7 +28304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="570" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A570" s="9" t="s">
         <v>100</v>
       </c>
@@ -28353,7 +28352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A571" s="6" t="s">
         <v>100</v>
       </c>
@@ -28401,7 +28400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A572" s="9" t="s">
         <v>100</v>
       </c>
@@ -28449,7 +28448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A573" s="6" t="s">
         <v>100</v>
       </c>
@@ -28497,7 +28496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A574" s="9" t="s">
         <v>100</v>
       </c>
@@ -28545,7 +28544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A575" s="6" t="s">
         <v>100</v>
       </c>
@@ -28593,7 +28592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A576" s="9" t="s">
         <v>100</v>
       </c>
@@ -28641,7 +28640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A577" s="6" t="s">
         <v>100</v>
       </c>
@@ -28689,7 +28688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A578" s="9" t="s">
         <v>100</v>
       </c>
@@ -28737,7 +28736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A579" s="6" t="s">
         <v>100</v>
       </c>
@@ -28785,7 +28784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A580" s="9" t="s">
         <v>100</v>
       </c>
@@ -28833,7 +28832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="581" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A581" s="6" t="s">
         <v>100</v>
       </c>
@@ -28881,7 +28880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A582" s="9" t="s">
         <v>100</v>
       </c>
@@ -28929,7 +28928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A583" s="6" t="s">
         <v>100</v>
       </c>
@@ -28977,7 +28976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A584" s="9" t="s">
         <v>100</v>
       </c>
@@ -29025,7 +29024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A585" s="6" t="s">
         <v>100</v>
       </c>
@@ -29073,7 +29072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A586" s="9" t="s">
         <v>100</v>
       </c>
@@ -29121,7 +29120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A587" s="6" t="s">
         <v>100</v>
       </c>
@@ -29169,7 +29168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A588" s="9" t="s">
         <v>100</v>
       </c>
@@ -29217,7 +29216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A589" s="6" t="s">
         <v>100</v>
       </c>
@@ -29265,7 +29264,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A590" s="9" t="s">
         <v>100</v>
       </c>
@@ -29313,7 +29312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A591" s="6" t="s">
         <v>100</v>
       </c>
@@ -29361,7 +29360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A592" s="9" t="s">
         <v>100</v>
       </c>
@@ -29409,7 +29408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A593" s="6" t="s">
         <v>100</v>
       </c>
@@ -29457,7 +29456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="594" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A594" s="9" t="s">
         <v>100</v>
       </c>
@@ -29505,7 +29504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="595" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A595" s="6" t="s">
         <v>100</v>
       </c>
@@ -29553,7 +29552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="596" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A596" s="9" t="s">
         <v>100</v>
       </c>
@@ -29601,7 +29600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A597" s="6" t="s">
         <v>100</v>
       </c>
@@ -29649,7 +29648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="598" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A598" s="9" t="s">
         <v>100</v>
       </c>
@@ -29697,7 +29696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="599" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A599" s="6" t="s">
         <v>100</v>
       </c>
@@ -29745,7 +29744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="600" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A600" s="9" t="s">
         <v>100</v>
       </c>
@@ -29793,7 +29792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="601" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A601" s="6" t="s">
         <v>100</v>
       </c>
@@ -29841,7 +29840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="602" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A602" s="9" t="s">
         <v>100</v>
       </c>
@@ -29889,7 +29888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="603" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A603" s="6" t="s">
         <v>100</v>
       </c>
@@ -29937,7 +29936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="604" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A604" s="9" t="s">
         <v>100</v>
       </c>
@@ -29985,7 +29984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="605" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A605" s="6" t="s">
         <v>100</v>
       </c>
@@ -30033,7 +30032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="606" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A606" s="9" t="s">
         <v>100</v>
       </c>
@@ -30081,7 +30080,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="607" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A607" s="6" t="s">
         <v>100</v>
       </c>
@@ -30129,7 +30128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="608" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A608" s="9" t="s">
         <v>100</v>
       </c>
@@ -30177,7 +30176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="609" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A609" s="6" t="s">
         <v>100</v>
       </c>
@@ -30225,7 +30224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="610" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A610" s="9" t="s">
         <v>100</v>
       </c>
@@ -30273,7 +30272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="611" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A611" s="6" t="s">
         <v>100</v>
       </c>
@@ -30321,7 +30320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="612" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A612" s="9" t="s">
         <v>100</v>
       </c>
@@ -30369,7 +30368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="613" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A613" s="6" t="s">
         <v>100</v>
       </c>
@@ -30417,7 +30416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="614" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A614" s="9" t="s">
         <v>100</v>
       </c>
@@ -30465,7 +30464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="615" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A615" s="6" t="s">
         <v>100</v>
       </c>
@@ -30513,7 +30512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="616" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A616" s="9" t="s">
         <v>100</v>
       </c>
@@ -30561,7 +30560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="617" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A617" s="6" t="s">
         <v>100</v>
       </c>
@@ -30609,7 +30608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="618" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A618" s="9" t="s">
         <v>100</v>
       </c>
@@ -30657,7 +30656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="619" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A619" s="6" t="s">
         <v>100</v>
       </c>
@@ -30705,7 +30704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="620" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A620" s="9" t="s">
         <v>100</v>
       </c>
@@ -30753,7 +30752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="621" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A621" s="6" t="s">
         <v>100</v>
       </c>
@@ -30801,7 +30800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="622" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A622" s="9" t="s">
         <v>100</v>
       </c>
@@ -30849,7 +30848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="623" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A623" s="6" t="s">
         <v>100</v>
       </c>
@@ -30897,7 +30896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="624" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A624" s="9" t="s">
         <v>100</v>
       </c>
@@ -30945,7 +30944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="625" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A625" s="6" t="s">
         <v>100</v>
       </c>
@@ -30993,7 +30992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="626" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A626" s="9" t="s">
         <v>100</v>
       </c>
@@ -31041,7 +31040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="627" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A627" s="6" t="s">
         <v>100</v>
       </c>
@@ -31089,7 +31088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="628" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A628" s="9" t="s">
         <v>100</v>
       </c>
@@ -31137,7 +31136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="629" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A629" s="6" t="s">
         <v>100</v>
       </c>
@@ -31185,7 +31184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="630" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A630" s="9" t="s">
         <v>100</v>
       </c>
@@ -31233,7 +31232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="631" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A631" s="6" t="s">
         <v>100</v>
       </c>
@@ -31281,7 +31280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="632" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A632" s="9" t="s">
         <v>100</v>
       </c>
@@ -31329,7 +31328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="633" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A633" s="6" t="s">
         <v>100</v>
       </c>
@@ -31377,7 +31376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="634" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A634" s="9" t="s">
         <v>100</v>
       </c>
@@ -31425,7 +31424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="635" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A635" s="6" t="s">
         <v>100</v>
       </c>
@@ -31473,7 +31472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="636" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A636" s="9" t="s">
         <v>100</v>
       </c>
@@ -31521,7 +31520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="637" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A637" s="6" t="s">
         <v>100</v>
       </c>
@@ -31569,7 +31568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="638" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A638" s="9" t="s">
         <v>100</v>
       </c>
@@ -31617,7 +31616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="639" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A639" s="6" t="s">
         <v>100</v>
       </c>
@@ -31665,7 +31664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="640" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A640" s="9" t="s">
         <v>100</v>
       </c>
@@ -31713,7 +31712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="641" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A641" s="6" t="s">
         <v>100</v>
       </c>
@@ -31761,7 +31760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="642" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A642" s="9" t="s">
         <v>100</v>
       </c>
@@ -31809,7 +31808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="643" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A643" s="6" t="s">
         <v>100</v>
       </c>
@@ -31857,7 +31856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="644" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A644" s="9" t="s">
         <v>100</v>
       </c>
@@ -31905,7 +31904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="645" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A645" s="6" t="s">
         <v>100</v>
       </c>
@@ -31953,7 +31952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="646" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A646" s="9" t="s">
         <v>100</v>
       </c>
@@ -32001,7 +32000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="647" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A647" s="6" t="s">
         <v>100</v>
       </c>
@@ -32049,7 +32048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="648" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A648" s="9" t="s">
         <v>100</v>
       </c>
@@ -32097,7 +32096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="649" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A649" s="6" t="s">
         <v>100</v>
       </c>
@@ -32145,7 +32144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="650" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A650" s="9" t="s">
         <v>100</v>
       </c>
@@ -32193,7 +32192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="651" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A651" s="6" t="s">
         <v>100</v>
       </c>
@@ -32241,7 +32240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="652" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A652" s="9" t="s">
         <v>100</v>
       </c>
@@ -32289,7 +32288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="653" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A653" s="6" t="s">
         <v>100</v>
       </c>
@@ -32337,7 +32336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="654" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A654" s="9" t="s">
         <v>100</v>
       </c>
@@ -32385,7 +32384,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="655" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A655" s="6" t="s">
         <v>100</v>
       </c>
@@ -32433,7 +32432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="656" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A656" s="9" t="s">
         <v>100</v>
       </c>
@@ -32481,7 +32480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="657" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A657" s="6" t="s">
         <v>100</v>
       </c>
@@ -32529,7 +32528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="658" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A658" s="9" t="s">
         <v>100</v>
       </c>
@@ -32577,7 +32576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="659" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A659" s="6" t="s">
         <v>100</v>
       </c>
@@ -32625,7 +32624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="660" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A660" s="9" t="s">
         <v>100</v>
       </c>
@@ -32673,7 +32672,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="661" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A661" s="6" t="s">
         <v>100</v>
       </c>
@@ -32721,7 +32720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="662" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A662" s="9" t="s">
         <v>100</v>
       </c>
@@ -32769,7 +32768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="663" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A663" s="6" t="s">
         <v>100</v>
       </c>
@@ -32817,7 +32816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="664" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A664" s="9" t="s">
         <v>100</v>
       </c>
@@ -32865,7 +32864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="665" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A665" s="6" t="s">
         <v>100</v>
       </c>
@@ -32913,7 +32912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="666" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A666" s="9" t="s">
         <v>100</v>
       </c>
@@ -32961,7 +32960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="667" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A667" s="6" t="s">
         <v>100</v>
       </c>
@@ -33009,7 +33008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="668" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A668" s="9" t="s">
         <v>100</v>
       </c>
@@ -33057,7 +33056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="669" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A669" s="6" t="s">
         <v>100</v>
       </c>
@@ -33105,7 +33104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="670" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A670" s="9" t="s">
         <v>100</v>
       </c>
@@ -33153,7 +33152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="671" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A671" s="6" t="s">
         <v>100</v>
       </c>
@@ -33201,7 +33200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="672" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A672" s="9" t="s">
         <v>100</v>
       </c>
@@ -33249,7 +33248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="673" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A673" s="6" t="s">
         <v>100</v>
       </c>
@@ -33297,7 +33296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="674" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A674" s="9" t="s">
         <v>100</v>
       </c>
@@ -33345,7 +33344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="675" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A675" s="6" t="s">
         <v>100</v>
       </c>
@@ -33393,7 +33392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="676" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A676" s="9" t="s">
         <v>100</v>
       </c>
@@ -33441,7 +33440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="677" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A677" s="6" t="s">
         <v>100</v>
       </c>
@@ -33489,7 +33488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="678" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A678" s="9" t="s">
         <v>100</v>
       </c>
@@ -33537,7 +33536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="679" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A679" s="6" t="s">
         <v>100</v>
       </c>
@@ -33585,7 +33584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="680" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A680" s="9" t="s">
         <v>100</v>
       </c>
@@ -33633,7 +33632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="681" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A681" s="6" t="s">
         <v>100</v>
       </c>
@@ -33681,7 +33680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="682" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A682" s="9" t="s">
         <v>100</v>
       </c>
@@ -33729,7 +33728,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="683" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A683" s="6" t="s">
         <v>100</v>
       </c>
@@ -33777,7 +33776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="684" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A684" s="9" t="s">
         <v>100</v>
       </c>
@@ -33825,7 +33824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="685" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A685" s="6" t="s">
         <v>100</v>
       </c>
@@ -33873,7 +33872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="686" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A686" s="9" t="s">
         <v>100</v>
       </c>
@@ -33921,7 +33920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="687" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A687" s="6" t="s">
         <v>100</v>
       </c>
@@ -33969,7 +33968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="688" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A688" s="9" t="s">
         <v>100</v>
       </c>
@@ -34017,7 +34016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="689" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A689" s="6" t="s">
         <v>100</v>
       </c>
@@ -34065,7 +34064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="690" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A690" s="9" t="s">
         <v>100</v>
       </c>
@@ -34113,7 +34112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="691" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A691" s="6" t="s">
         <v>100</v>
       </c>
@@ -34161,7 +34160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="692" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A692" s="9" t="s">
         <v>100</v>
       </c>
@@ -34209,7 +34208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="693" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A693" s="6" t="s">
         <v>100</v>
       </c>
@@ -34257,7 +34256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="694" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A694" s="9" t="s">
         <v>100</v>
       </c>
@@ -34305,7 +34304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="695" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A695" s="6" t="s">
         <v>100</v>
       </c>
@@ -34353,7 +34352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="696" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A696" s="9" t="s">
         <v>100</v>
       </c>
@@ -34401,7 +34400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="697" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A697" s="6" t="s">
         <v>100</v>
       </c>
@@ -34449,7 +34448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="698" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A698" s="9" t="s">
         <v>100</v>
       </c>
@@ -34497,7 +34496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="699" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A699" s="6" t="s">
         <v>100</v>
       </c>
@@ -34545,7 +34544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="700" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A700" s="9" t="s">
         <v>100</v>
       </c>
@@ -34593,7 +34592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="701" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A701" s="6" t="s">
         <v>100</v>
       </c>
@@ -34641,7 +34640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="702" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A702" s="9" t="s">
         <v>100</v>
       </c>
@@ -34689,7 +34688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="703" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A703" s="6" t="s">
         <v>100</v>
       </c>
@@ -34737,7 +34736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="704" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A704" s="9" t="s">
         <v>100</v>
       </c>
@@ -34785,7 +34784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="705" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A705" s="6" t="s">
         <v>100</v>
       </c>
@@ -34833,7 +34832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="706" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A706" s="9" t="s">
         <v>100</v>
       </c>
@@ -34881,7 +34880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="707" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A707" s="6" t="s">
         <v>100</v>
       </c>
@@ -34929,7 +34928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="708" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A708" s="9" t="s">
         <v>100</v>
       </c>
@@ -34977,7 +34976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="709" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A709" s="6" t="s">
         <v>100</v>
       </c>
@@ -35025,7 +35024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="710" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A710" s="9" t="s">
         <v>100</v>
       </c>
@@ -35073,7 +35072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="711" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A711" s="6" t="s">
         <v>100</v>
       </c>
@@ -35121,7 +35120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="712" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A712" s="9" t="s">
         <v>100</v>
       </c>
@@ -35169,7 +35168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="713" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A713" s="6" t="s">
         <v>100</v>
       </c>
@@ -35217,7 +35216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="714" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A714" s="9" t="s">
         <v>100</v>
       </c>
@@ -35265,7 +35264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="715" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A715" s="6" t="s">
         <v>100</v>
       </c>
@@ -35313,7 +35312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="716" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A716" s="9" t="s">
         <v>100</v>
       </c>
@@ -35361,7 +35360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="717" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A717" s="6" t="s">
         <v>100</v>
       </c>
@@ -35409,7 +35408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="718" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A718" s="9" t="s">
         <v>100</v>
       </c>
@@ -35457,7 +35456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="719" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A719" s="6" t="s">
         <v>100</v>
       </c>
@@ -35505,7 +35504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="720" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A720" s="9" t="s">
         <v>100</v>
       </c>
@@ -35553,7 +35552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="721" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A721" s="6" t="s">
         <v>100</v>
       </c>
@@ -35601,7 +35600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="722" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A722" s="9" t="s">
         <v>100</v>
       </c>
@@ -35649,7 +35648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="723" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A723" s="6" t="s">
         <v>100</v>
       </c>
@@ -35697,7 +35696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="724" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A724" s="9" t="s">
         <v>100</v>
       </c>
@@ -35745,7 +35744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="725" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A725" s="6" t="s">
         <v>100</v>
       </c>
@@ -35793,7 +35792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="726" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A726" s="9" t="s">
         <v>100</v>
       </c>
@@ -35841,7 +35840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="727" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A727" s="6" t="s">
         <v>100</v>
       </c>
@@ -35889,7 +35888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="728" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A728" s="9" t="s">
         <v>100</v>
       </c>
@@ -35937,7 +35936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="729" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A729" s="6" t="s">
         <v>100</v>
       </c>
@@ -35985,7 +35984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="730" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A730" s="9" t="s">
         <v>100</v>
       </c>
@@ -36033,7 +36032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="731" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A731" s="6" t="s">
         <v>100</v>
       </c>
@@ -36081,7 +36080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="732" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A732" s="9" t="s">
         <v>100</v>
       </c>
@@ -36129,7 +36128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="733" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A733" s="6" t="s">
         <v>100</v>
       </c>
@@ -36177,7 +36176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="734" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A734" s="9" t="s">
         <v>100</v>
       </c>
@@ -36225,7 +36224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="735" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A735" s="6" t="s">
         <v>100</v>
       </c>
@@ -36273,7 +36272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="736" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A736" s="9" t="s">
         <v>100</v>
       </c>
@@ -36321,7 +36320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="737" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A737" s="6" t="s">
         <v>100</v>
       </c>
@@ -36369,7 +36368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="738" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A738" s="9" t="s">
         <v>100</v>
       </c>
@@ -36417,7 +36416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="739" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A739" s="6" t="s">
         <v>100</v>
       </c>
@@ -36465,7 +36464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="740" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A740" s="9" t="s">
         <v>100</v>
       </c>
@@ -36513,7 +36512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="741" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A741" s="6" t="s">
         <v>100</v>
       </c>
@@ -36561,7 +36560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="742" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A742" s="9" t="s">
         <v>100</v>
       </c>
@@ -36609,7 +36608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="743" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A743" s="6" t="s">
         <v>100</v>
       </c>
@@ -36657,7 +36656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="744" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A744" s="9" t="s">
         <v>100</v>
       </c>
@@ -36705,7 +36704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="745" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A745" s="6" t="s">
         <v>100</v>
       </c>
@@ -36753,7 +36752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="746" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A746" s="9" t="s">
         <v>100</v>
       </c>
@@ -36801,7 +36800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="747" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A747" s="6" t="s">
         <v>100</v>
       </c>
@@ -36849,7 +36848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="748" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A748" s="9" t="s">
         <v>100</v>
       </c>
@@ -36897,7 +36896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="749" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A749" s="6" t="s">
         <v>100</v>
       </c>
@@ -36945,7 +36944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="750" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A750" s="9" t="s">
         <v>100</v>
       </c>
@@ -36993,7 +36992,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="751" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A751" s="6" t="s">
         <v>100</v>
       </c>
@@ -37041,7 +37040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="752" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A752" s="9" t="s">
         <v>100</v>
       </c>
@@ -37089,7 +37088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="753" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A753" s="6" t="s">
         <v>100</v>
       </c>
@@ -37137,7 +37136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="754" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A754" s="9" t="s">
         <v>100</v>
       </c>
@@ -37185,7 +37184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="755" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A755" s="6" t="s">
         <v>100</v>
       </c>
@@ -37233,7 +37232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="756" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A756" s="9" t="s">
         <v>100</v>
       </c>
@@ -37281,7 +37280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="757" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A757" s="6" t="s">
         <v>100</v>
       </c>
@@ -37329,7 +37328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="758" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A758" s="9" t="s">
         <v>100</v>
       </c>
@@ -37377,7 +37376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="759" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A759" s="6" t="s">
         <v>100</v>
       </c>
@@ -37425,7 +37424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="760" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A760" s="9" t="s">
         <v>100</v>
       </c>
@@ -37473,7 +37472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="761" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A761" s="6" t="s">
         <v>100</v>
       </c>
@@ -37521,7 +37520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="762" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A762" s="9" t="s">
         <v>100</v>
       </c>
@@ -37569,7 +37568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="763" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A763" s="6" t="s">
         <v>100</v>
       </c>
@@ -37617,7 +37616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="764" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A764" s="9" t="s">
         <v>100</v>
       </c>
@@ -37665,7 +37664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="765" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A765" s="6" t="s">
         <v>100</v>
       </c>
@@ -37713,7 +37712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="766" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A766" s="9" t="s">
         <v>100</v>
       </c>
@@ -37761,7 +37760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="767" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A767" s="6" t="s">
         <v>100</v>
       </c>
@@ -37809,7 +37808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="768" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A768" s="9" t="s">
         <v>100</v>
       </c>
@@ -37857,7 +37856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="769" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A769" s="6" t="s">
         <v>100</v>
       </c>
@@ -37905,7 +37904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="770" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A770" s="9" t="s">
         <v>100</v>
       </c>
@@ -37953,7 +37952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="771" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A771" s="6" t="s">
         <v>100</v>
       </c>
@@ -38001,7 +38000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="772" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A772" s="9" t="s">
         <v>100</v>
       </c>
@@ -38049,7 +38048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="773" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A773" s="6" t="s">
         <v>100</v>
       </c>
@@ -38097,7 +38096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="774" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A774" s="9" t="s">
         <v>100</v>
       </c>
@@ -38145,7 +38144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="775" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A775" s="6" t="s">
         <v>100</v>
       </c>
@@ -38193,7 +38192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="776" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A776" s="9" t="s">
         <v>100</v>
       </c>
@@ -38241,7 +38240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="777" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A777" s="6" t="s">
         <v>100</v>
       </c>
@@ -38289,7 +38288,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="778" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A778" s="9" t="s">
         <v>100</v>
       </c>
@@ -38337,7 +38336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="779" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A779" s="6" t="s">
         <v>100</v>
       </c>
@@ -38385,7 +38384,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="780" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A780" s="9" t="s">
         <v>100</v>
       </c>
@@ -38433,7 +38432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="781" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A781" s="6" t="s">
         <v>100</v>
       </c>
@@ -38481,7 +38480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="782" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A782" s="9" t="s">
         <v>100</v>
       </c>
@@ -38529,7 +38528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="783" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A783" s="6" t="s">
         <v>100</v>
       </c>
@@ -38577,7 +38576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="784" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A784" s="9" t="s">
         <v>100</v>
       </c>
@@ -38625,7 +38624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="785" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A785" s="6" t="s">
         <v>100</v>
       </c>
@@ -38673,7 +38672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="786" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A786" s="9" t="s">
         <v>100</v>
       </c>
@@ -38721,7 +38720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="787" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A787" s="6" t="s">
         <v>100</v>
       </c>
@@ -38817,7 +38816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="789" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A789" s="6" t="s">
         <v>100</v>
       </c>
@@ -38865,7 +38864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="790" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A790" s="9" t="s">
         <v>100</v>
       </c>
@@ -38913,7 +38912,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="791" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A791" s="6" t="s">
         <v>100</v>
       </c>
@@ -38961,7 +38960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="792" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A792" s="9" t="s">
         <v>100</v>
       </c>
@@ -39009,7 +39008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="793" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A793" s="6" t="s">
         <v>100</v>
       </c>
@@ -39057,7 +39056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="794" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A794" s="9" t="s">
         <v>100</v>
       </c>
@@ -39105,7 +39104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="795" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A795" s="6" t="s">
         <v>100</v>
       </c>
@@ -39153,7 +39152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="796" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A796" s="9" t="s">
         <v>100</v>
       </c>
@@ -39201,7 +39200,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="797" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A797" s="6" t="s">
         <v>100</v>
       </c>
@@ -39249,7 +39248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="798" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A798" s="9" t="s">
         <v>100</v>
       </c>
@@ -39297,7 +39296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="799" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A799" s="6" t="s">
         <v>100</v>
       </c>
@@ -39345,7 +39344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="800" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A800" s="9" t="s">
         <v>100</v>
       </c>
@@ -39393,7 +39392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="801" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A801" s="6" t="s">
         <v>100</v>
       </c>
@@ -39441,7 +39440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="802" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A802" s="9" t="s">
         <v>100</v>
       </c>
@@ -39489,7 +39488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="803" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A803" s="6" t="s">
         <v>100</v>
       </c>
@@ -39537,7 +39536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="804" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A804" s="9" t="s">
         <v>100</v>
       </c>
@@ -39585,7 +39584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="805" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A805" s="6" t="s">
         <v>100</v>
       </c>
@@ -39633,7 +39632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="806" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A806" s="9" t="s">
         <v>100</v>
       </c>
@@ -39681,7 +39680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="807" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A807" s="6" t="s">
         <v>100</v>
       </c>
@@ -39729,7 +39728,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="808" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A808" s="9" t="s">
         <v>100</v>
       </c>
@@ -39777,7 +39776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="809" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A809" s="6" t="s">
         <v>100</v>
       </c>
@@ -39825,7 +39824,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="810" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A810" s="9" t="s">
         <v>100</v>
       </c>
@@ -39873,7 +39872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="811" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A811" s="6" t="s">
         <v>100</v>
       </c>
@@ -39921,7 +39920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="812" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A812" s="9" t="s">
         <v>100</v>
       </c>
@@ -39969,7 +39968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="813" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A813" s="6" t="s">
         <v>100</v>
       </c>
@@ -40065,7 +40064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="815" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A815" s="6" t="s">
         <v>100</v>
       </c>
@@ -40113,7 +40112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="816" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A816" s="9" t="s">
         <v>100</v>
       </c>
@@ -40161,7 +40160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="817" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A817" s="6" t="s">
         <v>100</v>
       </c>
@@ -40209,7 +40208,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="818" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A818" s="9" t="s">
         <v>100</v>
       </c>
@@ -40257,7 +40256,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="819" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A819" s="6" t="s">
         <v>100</v>
       </c>
@@ -40305,7 +40304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="820" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A820" s="9" t="s">
         <v>100</v>
       </c>
@@ -40353,7 +40352,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="821" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A821" s="6" t="s">
         <v>100</v>
       </c>
@@ -40401,7 +40400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="822" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A822" s="9" t="s">
         <v>100</v>
       </c>
@@ -40449,7 +40448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="823" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A823" s="6" t="s">
         <v>100</v>
       </c>
@@ -40497,7 +40496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="824" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A824" s="9" t="s">
         <v>100</v>
       </c>
@@ -40545,7 +40544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="825" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A825" s="6" t="s">
         <v>100</v>
       </c>
@@ -40593,7 +40592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="826" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A826" s="9" t="s">
         <v>100</v>
       </c>
@@ -40641,7 +40640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="827" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A827" s="6" t="s">
         <v>100</v>
       </c>
@@ -40689,7 +40688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="828" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A828" s="9" t="s">
         <v>100</v>
       </c>
@@ -40737,7 +40736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="829" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A829" s="6" t="s">
         <v>100</v>
       </c>
@@ -40785,7 +40784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="830" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A830" s="9" t="s">
         <v>100</v>
       </c>
@@ -40833,7 +40832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="831" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A831" s="6" t="s">
         <v>100</v>
       </c>
@@ -40881,7 +40880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="832" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A832" s="9" t="s">
         <v>100</v>
       </c>
@@ -40929,7 +40928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="833" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A833" s="6" t="s">
         <v>100</v>
       </c>
@@ -40977,7 +40976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="834" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A834" s="9" t="s">
         <v>100</v>
       </c>
@@ -41025,7 +41024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="835" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A835" s="6" t="s">
         <v>100</v>
       </c>
@@ -41073,7 +41072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="836" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A836" s="9" t="s">
         <v>100</v>
       </c>
@@ -41121,7 +41120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="837" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A837" s="6" t="s">
         <v>100</v>
       </c>
@@ -41169,7 +41168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="838" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A838" s="9" t="s">
         <v>100</v>
       </c>
@@ -41217,7 +41216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="839" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A839" s="6" t="s">
         <v>100</v>
       </c>
@@ -41265,7 +41264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="840" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A840" s="9" t="s">
         <v>100</v>
       </c>
@@ -41313,7 +41312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="841" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A841" s="6" t="s">
         <v>100</v>
       </c>
@@ -41361,7 +41360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="842" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A842" s="9" t="s">
         <v>100</v>
       </c>
@@ -41409,7 +41408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="843" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A843" s="6" t="s">
         <v>100</v>
       </c>
@@ -41457,7 +41456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="844" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A844" s="9" t="s">
         <v>100</v>
       </c>
@@ -41505,7 +41504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="845" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A845" s="6" t="s">
         <v>100</v>
       </c>
@@ -41553,7 +41552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="846" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A846" s="9" t="s">
         <v>100</v>
       </c>
@@ -41601,7 +41600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="847" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A847" s="6" t="s">
         <v>100</v>
       </c>
@@ -41649,7 +41648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="848" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A848" s="9" t="s">
         <v>100</v>
       </c>
@@ -41697,7 +41696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="849" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A849" s="6" t="s">
         <v>100</v>
       </c>
@@ -41745,7 +41744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="850" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A850" s="9" t="s">
         <v>100</v>
       </c>
@@ -41793,7 +41792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="851" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A851" s="6" t="s">
         <v>100</v>
       </c>
@@ -41841,7 +41840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="852" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A852" s="9" t="s">
         <v>100</v>
       </c>
@@ -41889,7 +41888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="853" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A853" s="6" t="s">
         <v>100</v>
       </c>
@@ -41937,7 +41936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="854" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A854" s="9" t="s">
         <v>100</v>
       </c>
@@ -41985,7 +41984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="855" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A855" s="6" t="s">
         <v>100</v>
       </c>
@@ -42033,7 +42032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="856" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A856" s="9" t="s">
         <v>100</v>
       </c>
@@ -42081,7 +42080,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="857" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A857" s="6" t="s">
         <v>100</v>
       </c>
@@ -42129,7 +42128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="858" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A858" s="9" t="s">
         <v>100</v>
       </c>
@@ -42177,7 +42176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="859" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A859" s="6" t="s">
         <v>100</v>
       </c>
@@ -42225,7 +42224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="860" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A860" s="9" t="s">
         <v>100</v>
       </c>
@@ -42273,7 +42272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="861" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A861" s="6" t="s">
         <v>100</v>
       </c>
@@ -42321,7 +42320,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="862" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A862" s="9" t="s">
         <v>100</v>
       </c>
@@ -42369,7 +42368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="863" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A863" s="6" t="s">
         <v>100</v>
       </c>
@@ -42417,7 +42416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="864" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A864" s="9" t="s">
         <v>100</v>
       </c>
@@ -42465,7 +42464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="865" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A865" s="6" t="s">
         <v>100</v>
       </c>
@@ -42513,7 +42512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="866" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A866" s="9" t="s">
         <v>100</v>
       </c>
@@ -42561,7 +42560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="867" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A867" s="6" t="s">
         <v>100</v>
       </c>
@@ -42609,7 +42608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="868" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A868" s="9" t="s">
         <v>100</v>
       </c>
@@ -42657,7 +42656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="869" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A869" s="6" t="s">
         <v>100</v>
       </c>
@@ -42705,7 +42704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="870" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A870" s="9" t="s">
         <v>100</v>
       </c>
@@ -42753,7 +42752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="871" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A871" s="6" t="s">
         <v>100</v>
       </c>
@@ -42801,7 +42800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="872" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A872" s="9" t="s">
         <v>100</v>
       </c>
@@ -42849,7 +42848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="873" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A873" s="6" t="s">
         <v>100</v>
       </c>
@@ -42897,7 +42896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="874" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A874" s="9" t="s">
         <v>100</v>
       </c>
@@ -42945,7 +42944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="875" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A875" s="6" t="s">
         <v>100</v>
       </c>
@@ -42993,7 +42992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="876" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A876" s="9" t="s">
         <v>100</v>
       </c>
@@ -43041,7 +43040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="877" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A877" s="6" t="s">
         <v>100</v>
       </c>
@@ -43089,7 +43088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="878" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A878" s="9" t="s">
         <v>100</v>
       </c>
@@ -43137,7 +43136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="879" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A879" s="6" t="s">
         <v>100</v>
       </c>
@@ -43185,7 +43184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="880" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A880" s="9" t="s">
         <v>100</v>
       </c>
@@ -43233,7 +43232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="881" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A881" s="6" t="s">
         <v>100</v>
       </c>
@@ -43281,7 +43280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="882" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A882" s="9" t="s">
         <v>100</v>
       </c>
@@ -43329,7 +43328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="883" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A883" s="6" t="s">
         <v>100</v>
       </c>
@@ -43377,7 +43376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="884" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A884" s="9" t="s">
         <v>100</v>
       </c>
@@ -43425,7 +43424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="885" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A885" s="6" t="s">
         <v>100</v>
       </c>
@@ -43473,7 +43472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="886" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A886" s="9" t="s">
         <v>100</v>
       </c>
@@ -43521,7 +43520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="887" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A887" s="6" t="s">
         <v>100</v>
       </c>
@@ -43569,7 +43568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="888" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A888" s="9" t="s">
         <v>100</v>
       </c>
@@ -43617,7 +43616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="889" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A889" s="6" t="s">
         <v>100</v>
       </c>
@@ -43665,7 +43664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="890" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A890" s="9" t="s">
         <v>100</v>
       </c>
@@ -43713,7 +43712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="891" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A891" s="6" t="s">
         <v>100</v>
       </c>
@@ -43761,7 +43760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="892" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A892" s="9" t="s">
         <v>100</v>
       </c>
@@ -43809,7 +43808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="893" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A893" s="6" t="s">
         <v>100</v>
       </c>
@@ -43857,7 +43856,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="894" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A894" s="9" t="s">
         <v>100</v>
       </c>
@@ -43905,7 +43904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="895" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A895" s="6" t="s">
         <v>100</v>
       </c>
@@ -43953,7 +43952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="896" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A896" s="9" t="s">
         <v>100</v>
       </c>
@@ -44001,7 +44000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="897" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A897" s="6" t="s">
         <v>100</v>
       </c>
@@ -44049,7 +44048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="898" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A898" s="9" t="s">
         <v>100</v>
       </c>
@@ -44097,7 +44096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="899" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A899" s="6" t="s">
         <v>100</v>
       </c>
@@ -44145,7 +44144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="900" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A900" s="9" t="s">
         <v>100</v>
       </c>
@@ -44193,7 +44192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="901" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A901" s="6" t="s">
         <v>100</v>
       </c>
@@ -44241,7 +44240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="902" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A902" s="9" t="s">
         <v>100</v>
       </c>
@@ -44289,7 +44288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="903" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A903" s="6" t="s">
         <v>100</v>
       </c>
@@ -44337,7 +44336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="904" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A904" s="9" t="s">
         <v>100</v>
       </c>
@@ -44385,7 +44384,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="905" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A905" s="6" t="s">
         <v>100</v>
       </c>
@@ -44433,7 +44432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="906" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A906" s="9" t="s">
         <v>100</v>
       </c>
@@ -44481,7 +44480,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="907" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A907" s="6" t="s">
         <v>100</v>
       </c>
@@ -44529,7 +44528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="908" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A908" s="9" t="s">
         <v>100</v>
       </c>
@@ -44577,7 +44576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="909" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A909" s="6" t="s">
         <v>100</v>
       </c>
@@ -44625,7 +44624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="910" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A910" s="9" t="s">
         <v>100</v>
       </c>
@@ -44673,7 +44672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="911" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A911" s="6" t="s">
         <v>100</v>
       </c>
@@ -44721,7 +44720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="912" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A912" s="9" t="s">
         <v>100</v>
       </c>
@@ -44769,7 +44768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="913" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A913" s="6" t="s">
         <v>100</v>
       </c>
@@ -44817,7 +44816,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="914" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A914" s="9" t="s">
         <v>100</v>
       </c>
@@ -44865,7 +44864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="915" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A915" s="6" t="s">
         <v>100</v>
       </c>
@@ -44913,7 +44912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="916" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A916" s="9" t="s">
         <v>100</v>
       </c>
@@ -44961,7 +44960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="917" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A917" s="6" t="s">
         <v>100</v>
       </c>
@@ -45009,7 +45008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="918" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A918" s="9" t="s">
         <v>100</v>
       </c>
@@ -45057,7 +45056,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="919" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A919" s="6" t="s">
         <v>100</v>
       </c>
@@ -45105,7 +45104,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="920" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A920" s="9" t="s">
         <v>100</v>
       </c>
@@ -45153,7 +45152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="921" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A921" s="6" t="s">
         <v>100</v>
       </c>
@@ -45201,7 +45200,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="922" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A922" s="9" t="s">
         <v>100</v>
       </c>
@@ -45249,7 +45248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="923" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A923" s="6" t="s">
         <v>100</v>
       </c>
@@ -45297,7 +45296,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="924" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A924" s="9" t="s">
         <v>100</v>
       </c>
@@ -45345,7 +45344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="925" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A925" s="6" t="s">
         <v>100</v>
       </c>
@@ -45393,7 +45392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="926" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A926" s="9" t="s">
         <v>100</v>
       </c>
@@ -45441,7 +45440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="927" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A927" s="6" t="s">
         <v>100</v>
       </c>
@@ -45489,7 +45488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="928" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A928" s="9" t="s">
         <v>100</v>
       </c>
@@ -45537,7 +45536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="929" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A929" s="6" t="s">
         <v>100</v>
       </c>
@@ -45585,7 +45584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="930" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A930" s="9" t="s">
         <v>100</v>
       </c>
@@ -45633,7 +45632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="931" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A931" s="6" t="s">
         <v>100</v>
       </c>
@@ -45681,7 +45680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="932" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A932" s="9" t="s">
         <v>100</v>
       </c>
@@ -45729,7 +45728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="933" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A933" s="6" t="s">
         <v>100</v>
       </c>
@@ -45777,7 +45776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="934" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A934" s="9" t="s">
         <v>100</v>
       </c>
@@ -45825,7 +45824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="935" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A935" s="6" t="s">
         <v>100</v>
       </c>
@@ -45873,7 +45872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="936" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A936" s="9" t="s">
         <v>100</v>
       </c>
@@ -45921,7 +45920,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="937" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A937" s="6" t="s">
         <v>100</v>
       </c>
@@ -45969,7 +45968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="938" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A938" s="9" t="s">
         <v>100</v>
       </c>
@@ -46017,7 +46016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="939" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A939" s="6" t="s">
         <v>100</v>
       </c>
@@ -46065,7 +46064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="940" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A940" s="9" t="s">
         <v>100</v>
       </c>
@@ -46113,7 +46112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="941" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A941" s="6" t="s">
         <v>100</v>
       </c>
@@ -46161,7 +46160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="942" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A942" s="9" t="s">
         <v>100</v>
       </c>
@@ -46209,7 +46208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="943" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A943" s="6" t="s">
         <v>100</v>
       </c>
@@ -46257,7 +46256,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="944" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="944" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A944" s="9" t="s">
         <v>100</v>
       </c>
@@ -46305,7 +46304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="945" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="945" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A945" s="6" t="s">
         <v>100</v>
       </c>
@@ -46353,7 +46352,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="946" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="946" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A946" s="9" t="s">
         <v>100</v>
       </c>
@@ -46401,7 +46400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="947" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="947" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A947" s="6" t="s">
         <v>100</v>
       </c>
@@ -46449,7 +46448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="948" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="948" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A948" s="9" t="s">
         <v>100</v>
       </c>
@@ -46497,7 +46496,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="949" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="949" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A949" s="6" t="s">
         <v>100</v>
       </c>
@@ -46545,7 +46544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="950" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="950" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A950" s="9" t="s">
         <v>100</v>
       </c>
@@ -46593,7 +46592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="951" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="951" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A951" s="6" t="s">
         <v>100</v>
       </c>
@@ -46641,7 +46640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="952" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="952" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A952" s="9" t="s">
         <v>100</v>
       </c>
@@ -46689,7 +46688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="953" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="953" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A953" s="6" t="s">
         <v>100</v>
       </c>
@@ -46737,7 +46736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="954" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="954" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A954" s="9" t="s">
         <v>100</v>
       </c>
@@ -46785,7 +46784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="955" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="955" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A955" s="6" t="s">
         <v>100</v>
       </c>
@@ -46833,7 +46832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="956" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="956" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A956" s="9" t="s">
         <v>100</v>
       </c>
@@ -46881,7 +46880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="957" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="957" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A957" s="6" t="s">
         <v>100</v>
       </c>
@@ -46929,7 +46928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="958" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="958" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A958" s="9" t="s">
         <v>100</v>
       </c>
@@ -46977,7 +46976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="959" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="959" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A959" s="6" t="s">
         <v>100</v>
       </c>
@@ -47025,7 +47024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="960" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="960" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A960" s="9" t="s">
         <v>100</v>
       </c>
@@ -47073,7 +47072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="961" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="961" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A961" s="6" t="s">
         <v>100</v>
       </c>
@@ -47121,7 +47120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="962" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="962" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A962" s="9" t="s">
         <v>100</v>
       </c>
@@ -47169,7 +47168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="963" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="963" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A963" s="6" t="s">
         <v>100</v>
       </c>
@@ -47217,7 +47216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="964" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="964" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A964" s="9" t="s">
         <v>100</v>
       </c>
@@ -47265,7 +47264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="965" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A965" s="6" t="s">
         <v>100</v>
       </c>
@@ -47313,7 +47312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="966" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="966" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A966" s="9" t="s">
         <v>100</v>
       </c>
@@ -47361,7 +47360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="967" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="967" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A967" s="6" t="s">
         <v>100</v>
       </c>
@@ -47409,7 +47408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="968" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="968" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A968" s="9" t="s">
         <v>100</v>
       </c>
@@ -47457,7 +47456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="969" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="969" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A969" s="6" t="s">
         <v>100</v>
       </c>
@@ -47505,7 +47504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="970" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="970" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A970" s="9" t="s">
         <v>100</v>
       </c>
@@ -47553,7 +47552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="971" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="971" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A971" s="6" t="s">
         <v>100</v>
       </c>
@@ -47601,7 +47600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="972" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A972" s="9" t="s">
         <v>100</v>
       </c>
@@ -47649,7 +47648,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="973" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A973" s="6" t="s">
         <v>100</v>
       </c>
@@ -47697,7 +47696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="974" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A974" s="9" t="s">
         <v>100</v>
       </c>
@@ -47745,7 +47744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="975" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="975" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A975" s="6" t="s">
         <v>100</v>
       </c>
@@ -47793,7 +47792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="976" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="976" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A976" s="9" t="s">
         <v>100</v>
       </c>
@@ -47841,7 +47840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="977" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="977" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A977" s="6" t="s">
         <v>100</v>
       </c>
@@ -47889,7 +47888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="978" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A978" s="9" t="s">
         <v>100</v>
       </c>
@@ -47937,7 +47936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="979" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A979" s="6" t="s">
         <v>100</v>
       </c>
@@ -47985,7 +47984,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="980" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A980" s="9" t="s">
         <v>100</v>
       </c>
@@ -48033,7 +48032,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="981" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="981" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A981" s="6" t="s">
         <v>100</v>
       </c>
@@ -48081,7 +48080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="982" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="982" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A982" s="9" t="s">
         <v>100</v>
       </c>
@@ -48129,7 +48128,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="983" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="983" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A983" s="6" t="s">
         <v>100</v>
       </c>
@@ -48177,7 +48176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="984" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="984" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A984" s="9" t="s">
         <v>100</v>
       </c>
@@ -48225,7 +48224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="985" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="985" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A985" s="6" t="s">
         <v>100</v>
       </c>
@@ -48273,7 +48272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="986" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="986" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A986" s="9" t="s">
         <v>100</v>
       </c>
@@ -48321,7 +48320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="987" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="987" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A987" s="6" t="s">
         <v>100</v>
       </c>
@@ -48369,7 +48368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="988" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="988" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A988" s="9" t="s">
         <v>100</v>
       </c>
@@ -48417,7 +48416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="989" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="989" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A989" s="6" t="s">
         <v>100</v>
       </c>
@@ -48465,7 +48464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="990" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="990" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A990" s="9" t="s">
         <v>100</v>
       </c>
@@ -48513,7 +48512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="991" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="991" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A991" s="6" t="s">
         <v>100</v>
       </c>
@@ -48561,7 +48560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="992" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="992" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A992" s="9" t="s">
         <v>100</v>
       </c>
@@ -48609,7 +48608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="993" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="993" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A993" s="6" t="s">
         <v>100</v>
       </c>
@@ -48657,7 +48656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="994" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="994" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A994" s="9" t="s">
         <v>100</v>
       </c>
@@ -48705,7 +48704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="995" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="995" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A995" s="6" t="s">
         <v>100</v>
       </c>
@@ -48753,7 +48752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="996" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="996" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A996" s="9" t="s">
         <v>100</v>
       </c>
@@ -48801,7 +48800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="997" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="997" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A997" s="6" t="s">
         <v>100</v>
       </c>
@@ -48849,7 +48848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="998" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="998" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A998" s="9" t="s">
         <v>100</v>
       </c>
@@ -48897,7 +48896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="999" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="999" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A999" s="6" t="s">
         <v>100</v>
       </c>
@@ -48945,7 +48944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1000" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1000" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1000" s="9" t="s">
         <v>100</v>
       </c>
@@ -48993,7 +48992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1001" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1001" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1001" s="6" t="s">
         <v>100</v>
       </c>
@@ -49041,7 +49040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1002" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1002" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1002" s="9" t="s">
         <v>100</v>
       </c>
@@ -49089,7 +49088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1003" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1003" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1003" s="6" t="s">
         <v>100</v>
       </c>
@@ -49137,7 +49136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1004" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1004" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1004" s="9" t="s">
         <v>100</v>
       </c>
@@ -49185,7 +49184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1005" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1005" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1005" s="6" t="s">
         <v>100</v>
       </c>
@@ -49233,7 +49232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1006" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1006" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1006" s="9" t="s">
         <v>100</v>
       </c>
@@ -49281,7 +49280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1007" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1007" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1007" s="6" t="s">
         <v>100</v>
       </c>
@@ -49329,7 +49328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1008" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1008" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1008" s="9" t="s">
         <v>100</v>
       </c>
@@ -49377,7 +49376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1009" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1009" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1009" s="6" t="s">
         <v>100</v>
       </c>
@@ -49425,7 +49424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1010" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1010" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1010" s="9" t="s">
         <v>100</v>
       </c>
@@ -49473,7 +49472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1011" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1011" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1011" s="6" t="s">
         <v>100</v>
       </c>
@@ -49521,7 +49520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1012" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1012" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1012" s="9" t="s">
         <v>100</v>
       </c>
@@ -49569,7 +49568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1013" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1013" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1013" s="6" t="s">
         <v>100</v>
       </c>
@@ -49617,7 +49616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1014" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1014" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1014" s="9" t="s">
         <v>100</v>
       </c>
@@ -49665,7 +49664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1015" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1015" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1015" s="6" t="s">
         <v>100</v>
       </c>
@@ -49713,7 +49712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1016" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1016" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1016" s="9" t="s">
         <v>100</v>
       </c>
@@ -49761,7 +49760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1017" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1017" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1017" s="6" t="s">
         <v>100</v>
       </c>
@@ -49809,7 +49808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1018" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1018" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1018" s="9" t="s">
         <v>100</v>
       </c>
@@ -49857,7 +49856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1019" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1019" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1019" s="6" t="s">
         <v>100</v>
       </c>
@@ -49905,7 +49904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1020" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1020" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1020" s="9" t="s">
         <v>100</v>
       </c>
@@ -49953,7 +49952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1021" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1021" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1021" s="6" t="s">
         <v>100</v>
       </c>
@@ -50001,7 +50000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1022" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1022" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1022" s="9" t="s">
         <v>100</v>
       </c>
@@ -50049,7 +50048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1023" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1023" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1023" s="6" t="s">
         <v>100</v>
       </c>
@@ -50097,7 +50096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1024" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1024" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1024" s="9" t="s">
         <v>100</v>
       </c>
@@ -50145,7 +50144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1025" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1025" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1025" s="6" t="s">
         <v>100</v>
       </c>
@@ -50193,7 +50192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1026" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1026" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1026" s="9" t="s">
         <v>100</v>
       </c>
@@ -50241,7 +50240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1027" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1027" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1027" s="6" t="s">
         <v>100</v>
       </c>
@@ -50289,7 +50288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1028" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1028" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1028" s="9" t="s">
         <v>100</v>
       </c>
@@ -50337,7 +50336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1029" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1029" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1029" s="6" t="s">
         <v>100</v>
       </c>
@@ -50385,7 +50384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1030" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1030" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1030" s="9" t="s">
         <v>100</v>
       </c>
@@ -50433,7 +50432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1031" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1031" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1031" s="6" t="s">
         <v>100</v>
       </c>
@@ -50481,7 +50480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1032" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1032" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1032" s="9" t="s">
         <v>100</v>
       </c>
@@ -50529,7 +50528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1033" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1033" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1033" s="6" t="s">
         <v>100</v>
       </c>
@@ -50577,7 +50576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1034" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1034" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1034" s="9" t="s">
         <v>100</v>
       </c>
@@ -50626,18 +50625,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P1034" xr:uid="{812DFA3C-E692-41F9-A0B2-252AE404A69C}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Farias Villalvazo Julio Cesar"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Machine Safety fundamentals"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:P1034" xr:uid="{812DFA3C-E692-41F9-A0B2-252AE404A69C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
